--- a/Bases/Metas_Inscricoes_Upmat.xlsx
+++ b/Bases/Metas_Inscricoes_Upmat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djdan\Documents\GitHub\Dash-Upmat\Bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{933CEDFA-297D-4A0C-BDE2-AA3B0F3670E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F267714A-595C-46BA-979C-6465B10367C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{F1E2D47D-7B76-4F3F-ACBF-BB7F37B470B1}"/>
   </bookViews>
@@ -581,7 +581,7 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -592,7 +592,7 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
